--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,45 @@
       </c>
       <c r="I41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -542,7 +542,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -619,12 +619,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -797,7 +797,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -866,7 +866,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -905,12 +905,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -542,7 +542,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -619,12 +619,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -797,7 +797,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-10, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -866,7 +866,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -905,12 +905,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -542,7 +542,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -619,12 +619,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -797,7 +797,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-10, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -866,7 +866,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -905,12 +905,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-10, 2026-03-11, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -534,7 +534,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1353,14 +1353,24 @@
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.3958333333333333</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ConteoIntermedia</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ConteoSemanal</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,12 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +516,12 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +541,12 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +574,12 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,6 +599,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -584,6 +624,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -626,6 +672,12 @@
         <is>
           <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -658,6 +710,12 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,6 +758,12 @@
         <is>
           <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -720,6 +784,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -747,6 +817,12 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -774,6 +850,12 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -801,6 +883,12 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -820,6 +908,12 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -839,6 +933,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -870,6 +970,12 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -913,6 +1019,12 @@
           <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -947,6 +1059,12 @@
         <is>
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -967,6 +1085,12 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -986,6 +1110,12 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1028,6 +1158,12 @@
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1048,6 +1184,12 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1067,6 +1209,12 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1109,6 +1257,12 @@
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1137,6 +1291,12 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1156,6 +1316,12 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1187,6 +1353,12 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1206,6 +1378,12 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1248,6 +1426,12 @@
         <is>
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1268,6 +1452,12 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1310,6 +1500,12 @@
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1330,6 +1526,12 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1372,6 +1574,12 @@
         <is>
           <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1404,6 +1612,12 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1423,6 +1637,12 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1465,6 +1685,12 @@
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
+      </c>
+      <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1485,6 +1711,12 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1528,6 +1760,12 @@
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1570,6 +1808,12 @@
         <is>
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
+      </c>
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -1598,6 +1842,12 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -1636,6 +1886,12 @@
         <is>
           <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
+      </c>
+      <c r="J42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -570,12 +570,12 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -665,16 +665,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
@@ -694,7 +694,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -702,19 +702,31 @@
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -751,19 +763,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +825,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -846,7 +858,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -871,23 +883,31 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SABADO</t>
+          <t>JUEVES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-23, 2026-03-28, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -966,7 +986,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1011,12 +1031,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1052,12 +1072,12 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1151,12 +1171,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1250,12 +1270,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1287,7 +1307,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1349,7 +1369,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1419,16 +1439,16 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
@@ -1493,12 +1513,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -1567,12 +1587,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-12, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -1608,7 +1628,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1678,12 +1698,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -1752,12 +1772,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -1801,12 +1821,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -1838,7 +1858,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -1850,7 +1870,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>PRUEBA</t>
@@ -1879,12 +1903,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-12, 2026-03-13, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="J42" t="n">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,40 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>CLUSTER</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
@@ -491,10 +496,11 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -516,10 +522,11 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -541,10 +548,11 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -560,24 +568,25 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -599,10 +608,11 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -624,10 +634,11 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -643,40 +654,41 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
       <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -692,40 +704,41 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
       <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
         <v>4</v>
       </c>
     </row>
@@ -741,40 +754,41 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
       <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -796,10 +810,11 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -815,24 +830,25 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -848,24 +864,25 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,32 +898,33 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
       <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -928,10 +946,11 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -953,10 +972,11 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -972,28 +992,29 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1009,40 +1030,41 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
       <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1058,32 +1080,33 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
       <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1105,10 +1128,11 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1130,10 +1154,11 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1149,40 +1174,41 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
       <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1204,10 +1230,11 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1229,10 +1256,11 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1248,40 +1276,41 @@
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
       <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1297,24 +1326,25 @@
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>4</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1336,10 +1366,11 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1355,28 +1386,29 @@
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>4</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,10 +1430,11 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1417,40 +1450,41 @@
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>4</v>
-      </c>
       <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1472,10 +1506,11 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1491,40 +1526,41 @@
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>4</v>
-      </c>
       <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1546,10 +1582,11 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1565,40 +1602,41 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>4</v>
-      </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1614,28 +1652,29 @@
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>4</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1657,10 +1696,11 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1676,40 +1716,41 @@
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
       <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1731,10 +1772,11 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1750,40 +1792,41 @@
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>09:00:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>4</v>
-      </c>
       <c r="K39" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1799,40 +1842,41 @@
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>4</v>
-      </c>
       <c r="K40" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1848,24 +1892,25 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>4</v>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1881,40 +1926,41 @@
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>4</v>
-      </c>
       <c r="K42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,45 +434,50 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CLUSTER</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
@@ -497,10 +502,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -523,10 +529,11 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -549,10 +556,11 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -571,22 +579,27 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -609,10 +622,11 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -635,10 +649,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -657,38 +672,43 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
       <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -707,38 +727,43 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
       <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
         <v>4</v>
       </c>
     </row>
@@ -757,38 +782,43 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -811,10 +841,11 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,22 +864,27 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,22 +903,27 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -901,30 +942,35 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
       <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -947,10 +993,11 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -973,10 +1020,11 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -995,26 +1043,31 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1033,38 +1086,43 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
       <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1083,30 +1141,35 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
       <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1129,10 +1192,11 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1155,10 +1219,11 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1177,38 +1242,43 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
       <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1231,10 +1301,11 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1257,10 +1328,11 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1279,38 +1351,43 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
       <c r="L25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1329,22 +1406,27 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>4</v>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1367,10 +1449,11 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1389,26 +1472,31 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1431,10 +1519,11 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1453,38 +1542,43 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>4</v>
-      </c>
       <c r="L30" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1507,10 +1601,11 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1529,38 +1624,43 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>4</v>
-      </c>
       <c r="L32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1583,10 +1683,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1605,38 +1706,43 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>4</v>
-      </c>
       <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1655,26 +1761,31 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
+          <t>ZIPAQUIRA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>4</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1697,10 +1808,11 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1719,38 +1831,43 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
+          <t>CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>4</v>
-      </c>
       <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1773,10 +1890,11 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1795,38 +1913,43 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>09:00:00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>4</v>
-      </c>
       <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1845,38 +1968,43 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>4</v>
-      </c>
       <c r="L40" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1895,22 +2023,27 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
+          <t>ZENTRAL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="n">
-        <v>4</v>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1927,40 +2060,41 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>4</v>
-      </c>
       <c r="L42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,55 +429,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Director de obra</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ValidacionParametrización</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
@@ -494,19 +509,30 @@
           <t>ABADIA SAN RAFAEL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -521,19 +547,30 @@
           <t>ARAGON</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -548,19 +585,30 @@
           <t>BAVIERA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -575,32 +623,55 @@
           <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fabian Enrique Gutierrez Tole</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -614,19 +685,30 @@
           <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -641,19 +723,30 @@
           <t>CADIZ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -668,47 +761,62 @@
           <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Licette Tatiana Koop Santa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -723,47 +831,64 @@
           <t>EL CAMPO</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Ardila Castañeda</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>TRES QUEBRADAS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
         <v>4</v>
       </c>
     </row>
@@ -778,47 +903,62 @@
           <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Doriam Mayreth Sanchez Saenz</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>IBERIA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -833,19 +973,30 @@
           <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -860,32 +1011,55 @@
           <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Maicol David Sanchez Ortiz</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -899,32 +1073,55 @@
           <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nidia Esperanza Herrera Padilla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>ALSACIA RESERVADO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -938,39 +1135,54 @@
           <t>LA CABRERA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TRES QUEBRADAS</t>
+          <t>Ronald Forero</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>Martin Rafael Bohorquez Marrugo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
+          <t>TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -985,19 +1197,30 @@
           <t>LA CRUZ</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1012,19 +1235,30 @@
           <t>LA PALMA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1039,36 +1273,59 @@
           <t>LA PEÑA</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jose Alejandro Barcenas Moreno</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>TRES QUEBRADAS</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1082,47 +1339,62 @@
           <t>LA SCALA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Javier Manuel Gonzalez Angulo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>LA SCALA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1137,39 +1409,54 @@
           <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALSACIA RESERVADO</t>
+          <t>Pedro Mora</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>Nidia Esperanza Herrera Padilla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
+          <t>ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1184,19 +1471,30 @@
           <t>LINZ E1</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1211,19 +1509,30 @@
           <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1238,47 +1547,62 @@
           <t>LORCA</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Johanna Diaz Mora</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>IBERIA</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1293,19 +1617,30 @@
           <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1320,19 +1655,30 @@
           <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1347,47 +1693,62 @@
           <t>METROPOLI 30</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Yorleynis Montejo Ruiz</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>METROPOLI 30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1402,32 +1763,55 @@
           <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Juan Alberto Gutierrez Forero</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1441,19 +1825,30 @@
           <t>PASEO DE SEVILLA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1468,36 +1863,59 @@
           <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>ZIPAQUIRA</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>4</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1511,19 +1929,30 @@
           <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1538,47 +1967,62 @@
           <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jennifer Paola Lopez Vaca</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>IBERIA</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>LUNES</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>08:00:00</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1593,19 +2037,30 @@
           <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1620,47 +2075,62 @@
           <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jhon Alexander Guarin Reina</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1675,19 +2145,30 @@
           <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1702,47 +2183,62 @@
           <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Zuri Andreina Orduz Sepulveda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>ZIPAQUIRA</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>MARTES</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1757,36 +2253,59 @@
           <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Yuli Maribel Arias Cifuentes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>ZIPAQUIRA</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>4</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1800,19 +2319,30 @@
           <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1827,47 +2357,64 @@
           <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dario Acosta Rubiano</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>4</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1882,19 +2429,30 @@
           <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1909,47 +2467,62 @@
           <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mauricio Andres Cervantes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>TRES QUEBRADAS</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>09:00:00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>4</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1964,47 +2537,62 @@
           <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Leonardo de Jesus Guerrero Cabrera</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>NORTE</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>11:00:00</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>4</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2019,82 +2607,54 @@
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
+          <t>Pedro Mora</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Yenny Paola Munevar Peña</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>ZENTRAL</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>4</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>PRUEBA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>4</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,6 +2658,48 @@
         <v>4</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MALAGA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Entregas</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ronald Forero</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -1289,7 +1289,9 @@
           <t>Jose Alejandro Barcenas Moreno</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>TRES QUEBRADAS</t>
@@ -1297,7 +1299,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1310,10 +1312,14 @@
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MALAGA</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -1162,7 +1162,11 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>VIERNES</t>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -650,13 +650,21 @@
           <t>LUNES</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
@@ -664,7 +672,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O5" t="n">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2718,6 +2718,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOGOTA </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-10, 2026-02-14, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -667,16 +667,16 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -813,16 +813,16 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -885,12 +885,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -955,19 +955,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1055,12 +1055,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1108,21 +1108,29 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1183,12 +1191,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1331,12 +1339,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1401,12 +1409,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1454,21 +1462,29 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1609,12 +1625,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1755,12 +1771,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -1817,12 +1833,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -1921,12 +1937,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2029,16 +2045,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
         <v>4</v>
@@ -2137,12 +2153,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2245,12 +2261,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2311,12 +2327,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -2421,12 +2437,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -2529,12 +2545,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -2599,12 +2615,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -2661,12 +2677,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -2757,19 +2773,19 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-10, 2026-02-14, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-28</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28, 2026-03-30</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2788,6 +2788,64 @@
         <v>5</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRUEBA BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ramiro Gonzalez</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -2807,7 +2807,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ramiro Gonzalez</t>
+          <t>Juan Vargas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -2814,7 +2814,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -2819,28 +2819,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>VIERNES</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
         <v>4</v>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MARTES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -667,16 +667,16 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -813,16 +813,16 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -885,12 +885,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -955,19 +955,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1055,12 +1055,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1191,12 +1191,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -1833,12 +1833,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -1937,12 +1937,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2045,16 +2045,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
         <v>4</v>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2327,12 +2327,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -2677,12 +2677,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -2773,19 +2773,19 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28, 2026-03-30</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2810,7 +2810,11 @@
           <t>Juan Vargas</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ju</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
@@ -2831,12 +2835,12 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O44" t="n">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,12 +667,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -813,12 +813,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -885,12 +885,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1055,12 +1055,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1108,29 +1108,21 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1191,12 +1183,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1339,12 +1331,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1409,12 +1401,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1462,29 +1454,21 @@
           <t>JUEVES</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>VIERNES</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1625,12 +1609,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1771,12 +1755,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -1833,12 +1817,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -1937,12 +1921,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2045,12 +2029,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2153,12 +2137,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2261,12 +2245,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2327,12 +2311,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -2437,12 +2421,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -2545,12 +2529,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -2615,12 +2599,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -2677,12 +2661,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -2773,16 +2757,16 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
+          <t>2025-11-01, 2025-11-03, 2025-11-08, 2025-11-10, 2025-11-15, 2025-11-17, 2025-11-22, 2025-11-24, 2025-11-29</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
         <v>4</v>
@@ -2796,7 +2780,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRUEBA BARRANQUILLA</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2807,46 +2791,178 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Juan Vargas</t>
+          <t>Germán Baquero</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ju</t>
+          <t>Kelly Gutierrez</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>PUERTA DORADA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMARETTO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Abimael Padilla</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RIVERBAY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Orlando Iguaran</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>VIERNES</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>4</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>02:00:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2966,6 +2966,68 @@
         <v>4</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE SOLEIL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ejecución/Entregas</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Claudia Cruz</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Luisa Henao</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -667,12 +667,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -813,12 +813,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -885,12 +885,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1055,12 +1055,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1117,12 +1117,12 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1183,12 +1183,12 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1463,12 +1463,12 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -1817,12 +1817,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -1921,12 +1921,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2311,12 +2311,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -2661,12 +2661,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -2757,16 +2757,16 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-03, 2025-11-08, 2025-11-10, 2025-11-15, 2025-11-17, 2025-11-22, 2025-11-24, 2025-11-29</t>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2025-11-03, 2025-11-04, 2025-11-10, 2025-11-11, 2025-11-17, 2025-11-18, 2025-11-24, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
         <v>4</v>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -2885,12 +2885,12 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-07, 2025-11-13, 2025-11-14, 2025-11-20, 2025-11-21, 2025-11-27, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-21, 2025-11-22, 2025-11-28, 2025-11-29</t>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-06, 2025-11-12, 2025-11-13, 2025-11-19, 2025-11-20, 2025-11-26, 2025-11-27</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -3013,12 +3013,12 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-12, 2025-11-18, 2025-11-19, 2025-11-25, 2025-11-26</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="O47" t="n">
